--- a/data/trans_orig/MCS12_SP_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2007</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>235633</t>
+          <t>240157</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>288844</t>
+          <t>289060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>303112</t>
+          <t>302964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>354501</t>
+          <t>353349</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>554048</t>
+          <t>558358</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>627686</t>
+          <t>630841</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405168</t>
+          <t>404952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>458379</t>
+          <t>453855</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333850</t>
+          <t>335002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>385239</t>
+          <t>385387</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>754677</t>
+          <t>751522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>828315</t>
+          <t>824005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>383323</t>
+          <t>383462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>446749</t>
+          <t>447731</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>514610</t>
+          <t>511750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>579184</t>
+          <t>576581</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>914958</t>
+          <t>915956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1003846</t>
+          <t>1002551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>515051</t>
+          <t>514069</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>578477</t>
+          <t>578338</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389209</t>
+          <t>391812</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>453783</t>
+          <t>456643</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>926347</t>
+          <t>927642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1015235</t>
+          <t>1014237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>269698</t>
+          <t>272322</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>323841</t>
+          <t>324317</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>348117</t>
+          <t>349964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>399941</t>
+          <t>399150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>634418</t>
+          <t>631264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>710226</t>
+          <t>708726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>354668</t>
+          <t>354192</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>408811</t>
+          <t>406187</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283900</t>
+          <t>284691</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335724</t>
+          <t>333877</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652124</t>
+          <t>653624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>727932</t>
+          <t>731086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>413238</t>
+          <t>410470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>471504</t>
+          <t>473198</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>550355</t>
+          <t>550109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>612806</t>
+          <t>612492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>976670</t>
+          <t>972306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1062648</t>
+          <t>1064060</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>470718</t>
+          <t>469024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>528984</t>
+          <t>531752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>425806</t>
+          <t>426120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>488257</t>
+          <t>488503</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>918186</t>
+          <t>916774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1004164</t>
+          <t>1008528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1356877</t>
+          <t>1359326</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1473889</t>
+          <t>1474346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1773088</t>
+          <t>1770768</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1890301</t>
+          <t>1893868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3167492</t>
+          <t>3159395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3328852</t>
+          <t>3321312</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1802654</t>
+          <t>1802197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1919666</t>
+          <t>1917217</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1488896</t>
+          <t>1485329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1606109</t>
+          <t>1608429</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3326889</t>
+          <t>3334429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3488249</t>
+          <t>3496346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,53%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2012</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>324053</t>
+          <t>323866</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>376629</t>
+          <t>377157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>436815</t>
+          <t>439185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>488794</t>
+          <t>490055</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>772083</t>
+          <t>773557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>849610</t>
+          <t>847826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,54%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326840</t>
+          <t>326312</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379416</t>
+          <t>379603</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>208256</t>
+          <t>206995</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260235</t>
+          <t>257865</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>550909</t>
+          <t>552693</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>628436</t>
+          <t>626962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>452860</t>
+          <t>456106</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>521673</t>
+          <t>521008</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>566643</t>
+          <t>566425</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>631274</t>
+          <t>633564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1042662</t>
+          <t>1041254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1137784</t>
+          <t>1129129</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496274</t>
+          <t>496939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>565087</t>
+          <t>561841</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>400910</t>
+          <t>398620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>465541</t>
+          <t>465759</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>912347</t>
+          <t>921002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1007469</t>
+          <t>1008877</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>316416</t>
+          <t>315926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>374182</t>
+          <t>372782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>431859</t>
+          <t>430102</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>487484</t>
+          <t>488648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>762822</t>
+          <t>765617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>843906</t>
+          <t>847737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>383441</t>
+          <t>384841</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>441207</t>
+          <t>441697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289690</t>
+          <t>288526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>345315</t>
+          <t>347072</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>690891</t>
+          <t>687060</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>771975</t>
+          <t>769180</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>466271</t>
+          <t>464833</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>644588</t>
+          <t>646508</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>710681</t>
+          <t>708020</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1124888</t>
+          <t>1131252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1221982</t>
+          <t>1216824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,85%</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>481468</t>
+          <t>482906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>341220</t>
+          <t>343881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>407313</t>
+          <t>405393</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>777658</t>
+          <t>782816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>874752</t>
+          <t>868388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1620190</t>
+          <t>1621155</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1738378</t>
+          <t>1735304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2141823</t>
+          <t>2141157</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2259257</t>
+          <t>2255406</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3790831</t>
+          <t>3799360</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3959656</t>
+          <t>3968661</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1688401</t>
+          <t>1691475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1806589</t>
+          <t>1805624</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1299052</t>
+          <t>1302903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1416486</t>
+          <t>1417152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3025432</t>
+          <t>3016427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3194257</t>
+          <t>3185728</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2016</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>300620</t>
+          <t>300964</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>353802</t>
+          <t>355276</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>356623</t>
+          <t>356622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>406775</t>
+          <t>406707</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>672505</t>
+          <t>671943</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>746482</t>
+          <t>745635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>320998</t>
+          <t>319524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>374180</t>
+          <t>373836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266064</t>
+          <t>266132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>316216</t>
+          <t>316217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>601157</t>
+          <t>602004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>675134</t>
+          <t>675696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,14%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>444673</t>
+          <t>447715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>507845</t>
+          <t>511548</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>529954</t>
+          <t>530833</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>597485</t>
+          <t>597590</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>993415</t>
+          <t>995956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1084291</t>
+          <t>1088156</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514586</t>
+          <t>510883</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>577758</t>
+          <t>574716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>445428</t>
+          <t>445323</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512959</t>
+          <t>512080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>981053</t>
+          <t>977188</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1071929</t>
+          <t>1069388</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>298762</t>
+          <t>296934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>352911</t>
+          <t>349530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>357064</t>
+          <t>356655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>413195</t>
+          <t>412156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>667316</t>
+          <t>668974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>747609</t>
+          <t>746458</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406641</t>
+          <t>410022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>460790</t>
+          <t>462618</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>371816</t>
+          <t>372855</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>427947</t>
+          <t>428356</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>796954</t>
+          <t>798105</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>877247</t>
+          <t>875589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>477873</t>
+          <t>477706</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>537082</t>
+          <t>537613</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>583919</t>
+          <t>584382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>646431</t>
+          <t>647360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1078004</t>
+          <t>1076255</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1167391</t>
+          <t>1167371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>400485</t>
+          <t>399954</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>459694</t>
+          <t>459861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>397348</t>
+          <t>396419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459860</t>
+          <t>459397</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>813955</t>
+          <t>813975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>903342</t>
+          <t>905091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1575082</t>
+          <t>1578751</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1691855</t>
+          <t>1701411</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1882208</t>
+          <t>1884984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2005086</t>
+          <t>2012236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3498469</t>
+          <t>3483912</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3664912</t>
+          <t>3659063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1702495</t>
+          <t>1692939</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1819268</t>
+          <t>1815599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1539456</t>
+          <t>1532306</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1662334</t>
+          <t>1659558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3273980</t>
+          <t>3279829</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3440423</t>
+          <t>3454980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,79%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2023</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>217639</t>
+          <t>217855</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>271037</t>
+          <t>269408</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>294772</t>
+          <t>295509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>334036</t>
+          <t>334360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>522879</t>
+          <t>518851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>591245</t>
+          <t>590716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>359127</t>
+          <t>360756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412525</t>
+          <t>412309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335825</t>
+          <t>335501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>375089</t>
+          <t>374352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>708779</t>
+          <t>709308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>777145</t>
+          <t>781173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>211768</t>
+          <t>208024</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>506478</t>
+          <t>506050</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>436736</t>
+          <t>438064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>491344</t>
+          <t>489229</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>575942</t>
+          <t>548313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>980036</t>
+          <t>981945</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,86%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681834</t>
+          <t>682262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>976544</t>
+          <t>980288</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461495</t>
+          <t>463610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516103</t>
+          <t>514775</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1161115</t>
+          <t>1159206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1565209</t>
+          <t>1592838</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>256659</t>
+          <t>255292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>315230</t>
+          <t>316351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>434777</t>
+          <t>430182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>728289</t>
+          <t>734312</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>706367</t>
+          <t>708655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1115244</t>
+          <t>1131041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387096</t>
+          <t>385975</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>445667</t>
+          <t>447034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>203342</t>
+          <t>197319</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>496854</t>
+          <t>501449</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>518712</t>
+          <t>502915</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>927589</t>
+          <t>925301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,63%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>376904</t>
+          <t>376903</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>445197</t>
+          <t>441545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>586370</t>
+          <t>584115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>719329</t>
+          <t>717914</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>982793</t>
+          <t>979189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1137565</t>
+          <t>1152127</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>477712</t>
+          <t>481364</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>546005</t>
+          <t>546006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>369944</t>
+          <t>371359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502903</t>
+          <t>505158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>874617</t>
+          <t>860055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1029389</t>
+          <t>1032993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>976902</t>
+          <t>1052445</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1447636</t>
+          <t>1456307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1823309</t>
+          <t>1827309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2243155</t>
+          <t>2268094</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2972898</t>
+          <t>2972143</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3602461</t>
+          <t>3633796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1996075</t>
+          <t>1987404</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2466809</t>
+          <t>2391266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1400448</t>
+          <t>1375509</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1820294</t>
+          <t>1816294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3484853</t>
+          <t>3453518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4114416</t>
+          <t>4115171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/MCS12_SP_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>240157</t>
+          <t>236741</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>289060</t>
+          <t>288864</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>302964</t>
+          <t>303837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>353349</t>
+          <t>355689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>558358</t>
+          <t>555541</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>630841</t>
+          <t>626877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404952</t>
+          <t>405148</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453855</t>
+          <t>457271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335002</t>
+          <t>332662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>385387</t>
+          <t>384514</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>751522</t>
+          <t>755486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>824005</t>
+          <t>826822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>383462</t>
+          <t>381707</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>447731</t>
+          <t>445235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>511750</t>
+          <t>514838</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>576581</t>
+          <t>580535</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>915956</t>
+          <t>917871</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1002551</t>
+          <t>1008975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,27%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514069</t>
+          <t>516565</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>578338</t>
+          <t>580093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>391812</t>
+          <t>387858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>456643</t>
+          <t>453555</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>927642</t>
+          <t>921218</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1014237</t>
+          <t>1012322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>272322</t>
+          <t>269281</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>324317</t>
+          <t>322011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>349964</t>
+          <t>347748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>399150</t>
+          <t>401317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>631264</t>
+          <t>636492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>708726</t>
+          <t>710575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>354192</t>
+          <t>356498</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>406187</t>
+          <t>409228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>284691</t>
+          <t>282524</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333877</t>
+          <t>336093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653624</t>
+          <t>651775</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>731086</t>
+          <t>725858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,28%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>410470</t>
+          <t>409030</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>473198</t>
+          <t>470106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>550109</t>
+          <t>546154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>612492</t>
+          <t>610344</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>972306</t>
+          <t>973847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1064060</t>
+          <t>1066708</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>469024</t>
+          <t>472116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>531752</t>
+          <t>533192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>426120</t>
+          <t>428268</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>488503</t>
+          <t>492458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>916774</t>
+          <t>914126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1008528</t>
+          <t>1006987</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,84%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1359326</t>
+          <t>1359732</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1474346</t>
+          <t>1472819</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1770768</t>
+          <t>1773654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1893868</t>
+          <t>1890895</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3159395</t>
+          <t>3161364</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3321312</t>
+          <t>3326987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1802197</t>
+          <t>1803724</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1917217</t>
+          <t>1916811</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1485329</t>
+          <t>1488302</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1608429</t>
+          <t>1605543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3334429</t>
+          <t>3328754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3496346</t>
+          <t>3494377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>323866</t>
+          <t>319857</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>377157</t>
+          <t>376046</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>439185</t>
+          <t>436244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>490055</t>
+          <t>486969</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>773557</t>
+          <t>773551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>847826</t>
+          <t>846552</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326312</t>
+          <t>327423</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379603</t>
+          <t>383612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>206995</t>
+          <t>210081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257865</t>
+          <t>260806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>552693</t>
+          <t>553967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>626962</t>
+          <t>626968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>456106</t>
+          <t>456012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>521008</t>
+          <t>522804</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>566425</t>
+          <t>567302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>633564</t>
+          <t>631840</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1041254</t>
+          <t>1037977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1129129</t>
+          <t>1130277</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496939</t>
+          <t>495143</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>561841</t>
+          <t>561935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>398620</t>
+          <t>400344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>465759</t>
+          <t>464882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>921002</t>
+          <t>919854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1008877</t>
+          <t>1012154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>315926</t>
+          <t>313983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>372782</t>
+          <t>372715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>430102</t>
+          <t>432416</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>488648</t>
+          <t>489269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>765617</t>
+          <t>763485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>847737</t>
+          <t>847172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>384841</t>
+          <t>384908</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>441697</t>
+          <t>443640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>288526</t>
+          <t>287905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>347072</t>
+          <t>344758</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>687060</t>
+          <t>687625</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>769180</t>
+          <t>771312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>464833</t>
+          <t>469751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>529818</t>
+          <t>527939</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>646508</t>
+          <t>647129</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>708020</t>
+          <t>709027</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1131252</t>
+          <t>1127994</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1216824</t>
+          <t>1220551</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,04%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>417921</t>
+          <t>419800</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>482906</t>
+          <t>477988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343881</t>
+          <t>342874</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>405393</t>
+          <t>404772</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>782816</t>
+          <t>779089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>868388</t>
+          <t>871646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1621155</t>
+          <t>1617919</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1735304</t>
+          <t>1741217</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2141157</t>
+          <t>2141732</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2255406</t>
+          <t>2263726</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3799360</t>
+          <t>3797016</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3968661</t>
+          <t>3961862</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,72%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1691475</t>
+          <t>1685562</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1805624</t>
+          <t>1808860</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1302903</t>
+          <t>1294583</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1417152</t>
+          <t>1416577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3016427</t>
+          <t>3023226</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3185728</t>
+          <t>3188072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>300964</t>
+          <t>299788</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>355276</t>
+          <t>353106</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>406707</t>
+          <t>408046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>671943</t>
+          <t>669080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>745635</t>
+          <t>742067</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,06%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>319524</t>
+          <t>321694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373836</t>
+          <t>375012</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266132</t>
+          <t>264793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>602004</t>
+          <t>605572</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>675696</t>
+          <t>678559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>447715</t>
+          <t>443007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>511548</t>
+          <t>509702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>530833</t>
+          <t>527302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>597590</t>
+          <t>595253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>995956</t>
+          <t>990067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1088156</t>
+          <t>1081321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>510883</t>
+          <t>512729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>574716</t>
+          <t>579424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>445323</t>
+          <t>447660</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512080</t>
+          <t>515611</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>977188</t>
+          <t>984023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1069388</t>
+          <t>1075277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>296934</t>
+          <t>297629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>349530</t>
+          <t>352063</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>356655</t>
+          <t>354993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>412156</t>
+          <t>410194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>668974</t>
+          <t>668734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>746458</t>
+          <t>748249</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,44%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>410022</t>
+          <t>407489</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462618</t>
+          <t>461923</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>372855</t>
+          <t>374817</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>428356</t>
+          <t>430018</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>798105</t>
+          <t>796314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>875589</t>
+          <t>875829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>477706</t>
+          <t>475372</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>537613</t>
+          <t>541820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>584382</t>
+          <t>582735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>647360</t>
+          <t>645174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1076255</t>
+          <t>1076190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1167371</t>
+          <t>1165712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,83%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>399954</t>
+          <t>395747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>459861</t>
+          <t>462195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>396419</t>
+          <t>398605</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459397</t>
+          <t>461044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>813975</t>
+          <t>815634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>905091</t>
+          <t>905156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1578751</t>
+          <t>1569963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1701411</t>
+          <t>1684833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1884984</t>
+          <t>1877885</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2012236</t>
+          <t>2002874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3483912</t>
+          <t>3488953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3659063</t>
+          <t>3660935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,76%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1692939</t>
+          <t>1709517</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1815599</t>
+          <t>1824387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1532306</t>
+          <t>1541668</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1659558</t>
+          <t>1666657</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3279829</t>
+          <t>3277957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3454980</t>
+          <t>3449939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>243583</t>
+          <t>263931</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>217855</t>
+          <t>238369</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>269408</t>
+          <t>291934</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>314459</t>
+          <t>341102</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>295509</t>
+          <t>316701</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>334360</t>
+          <t>363783</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>558042</t>
+          <t>605033</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>518851</t>
+          <t>570454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>590716</t>
+          <t>638509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>386581</t>
+          <t>420840</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360756</t>
+          <t>392837</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412309</t>
+          <t>446402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>355402</t>
+          <t>385929</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335501</t>
+          <t>363248</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>374352</t>
+          <t>410330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>741982</t>
+          <t>806769</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>709308</t>
+          <t>773293</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>781173</t>
+          <t>841348</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>630164</t>
+          <t>684771</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>630164</t>
+          <t>684771</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>630164</t>
+          <t>684771</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>669861</t>
+          <t>727031</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>669861</t>
+          <t>727031</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>669861</t>
+          <t>727031</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1300024</t>
+          <t>1411802</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1300024</t>
+          <t>1411802</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1300024</t>
+          <t>1411802</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>391503</t>
+          <t>436982</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>208024</t>
+          <t>399257</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>506050</t>
+          <t>473246</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>464161</t>
+          <t>523193</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>438064</t>
+          <t>491622</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>489229</t>
+          <t>551924</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>855664</t>
+          <t>960176</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>548313</t>
+          <t>917847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>981945</t>
+          <t>1010034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>796809</t>
+          <t>606849</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>682262</t>
+          <t>570585</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>980288</t>
+          <t>644574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>488678</t>
+          <t>541918</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463610</t>
+          <t>513187</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514775</t>
+          <t>573489</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1285487</t>
+          <t>1148767</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1159206</t>
+          <t>1098909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1592838</t>
+          <t>1191096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>56,48%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1188312</t>
+          <t>1043831</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1188312</t>
+          <t>1043831</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1188312</t>
+          <t>1043831</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>952839</t>
+          <t>1065111</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>952839</t>
+          <t>1065111</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>952839</t>
+          <t>1065111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2141151</t>
+          <t>2108943</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2141151</t>
+          <t>2108943</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2141151</t>
+          <t>2108943</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>284976</t>
+          <t>321866</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>255292</t>
+          <t>288541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>316351</t>
+          <t>352546</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>554651</t>
+          <t>408582</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>430182</t>
+          <t>381681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>734312</t>
+          <t>435265</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>839626</t>
+          <t>730448</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>708655</t>
+          <t>691516</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1131041</t>
+          <t>772153</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>417350</t>
+          <t>478479</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>385975</t>
+          <t>447799</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>447034</t>
+          <t>511804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>376980</t>
+          <t>401821</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>197319</t>
+          <t>375138</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>501449</t>
+          <t>428722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>794330</t>
+          <t>880301</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>502915</t>
+          <t>838596</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>925301</t>
+          <t>919233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>57,07%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>800345</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>800345</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>800345</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931631</t>
+          <t>810403</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931631</t>
+          <t>810403</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931631</t>
+          <t>810403</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1633956</t>
+          <t>1610749</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1633956</t>
+          <t>1610749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1633956</t>
+          <t>1610749</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>410482</t>
+          <t>448203</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>376903</t>
+          <t>417225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>441545</t>
+          <t>481930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>627160</t>
+          <t>613311</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>584115</t>
+          <t>585965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>717914</t>
+          <t>643002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1037641</t>
+          <t>1061514</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>979189</t>
+          <t>1014067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1152127</t>
+          <t>1103709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>52,58%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>512427</t>
+          <t>537952</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>481364</t>
+          <t>504225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>546006</t>
+          <t>568930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>462113</t>
+          <t>499771</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>371359</t>
+          <t>470080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>505158</t>
+          <t>527117</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>974541</t>
+          <t>1037723</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>860055</t>
+          <t>995528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1032993</t>
+          <t>1085170</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,69%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>922909</t>
+          <t>986155</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>922909</t>
+          <t>986155</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>922909</t>
+          <t>986155</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1089273</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1089273</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1089273</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012182</t>
+          <t>2099237</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012182</t>
+          <t>2099237</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012182</t>
+          <t>2099237</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1330544</t>
+          <t>1470982</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1052445</t>
+          <t>1407074</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1456307</t>
+          <t>1533452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1960429</t>
+          <t>1886188</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1827309</t>
+          <t>1836258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2268094</t>
+          <t>1940212</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3290973</t>
+          <t>3357170</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2972143</t>
+          <t>3275867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3633796</t>
+          <t>3442213</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2113167</t>
+          <t>2044121</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1987404</t>
+          <t>1981651</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2391266</t>
+          <t>2108029</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1683174</t>
+          <t>1829439</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1375509</t>
+          <t>1775415</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1816294</t>
+          <t>1879369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,17 +8124,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3796341</t>
+          <t>3873560</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3453518</t>
+          <t>3788517</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4115171</t>
+          <t>3954863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
